--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123084743</v>
+        <v>123083226</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460789</v>
+        <v>460899</v>
       </c>
       <c r="R2" t="n">
-        <v>6866588</v>
+        <v>6866720</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123084848</v>
+        <v>123083889</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460770</v>
+        <v>460883</v>
       </c>
       <c r="R3" t="n">
-        <v>6866610</v>
+        <v>6866590</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083226</v>
+        <v>123084743</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460899</v>
+        <v>460789</v>
       </c>
       <c r="R4" t="n">
-        <v>6866720</v>
+        <v>6866588</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123083889</v>
+        <v>123084848</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460883</v>
+        <v>460770</v>
       </c>
       <c r="R5" t="n">
-        <v>6866590</v>
+        <v>6866610</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123083226</v>
+        <v>123084848</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460899</v>
+        <v>460770</v>
       </c>
       <c r="R2" t="n">
-        <v>6866720</v>
+        <v>6866610</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083889</v>
+        <v>123083427</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>77694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460883</v>
+        <v>460885</v>
       </c>
       <c r="R3" t="n">
-        <v>6866590</v>
+        <v>6866626</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123084743</v>
+        <v>123083574</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460789</v>
+        <v>460893</v>
       </c>
       <c r="R4" t="n">
-        <v>6866588</v>
+        <v>6866619</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123084848</v>
+        <v>123084743</v>
       </c>
       <c r="B5" t="n">
         <v>78502</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460770</v>
+        <v>460789</v>
       </c>
       <c r="R5" t="n">
-        <v>6866610</v>
+        <v>6866588</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123084224</v>
+        <v>123083889</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460857</v>
+        <v>460883</v>
       </c>
       <c r="R6" t="n">
-        <v>6866603</v>
+        <v>6866590</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084942</v>
+        <v>123084224</v>
       </c>
       <c r="B7" t="n">
-        <v>77694</v>
+        <v>78502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460739</v>
+        <v>460857</v>
       </c>
       <c r="R7" t="n">
-        <v>6866616</v>
+        <v>6866603</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123084843</v>
+        <v>123085253</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460770</v>
+        <v>460766</v>
       </c>
       <c r="R8" t="n">
-        <v>6866610</v>
+        <v>6866660</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084785</v>
+        <v>123084843</v>
       </c>
       <c r="B9" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460787</v>
+        <v>460770</v>
       </c>
       <c r="R9" t="n">
-        <v>6866602</v>
+        <v>6866610</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123085253</v>
+        <v>123084899</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460766</v>
+        <v>460751</v>
       </c>
       <c r="R10" t="n">
-        <v>6866660</v>
+        <v>6866595</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123083427</v>
+        <v>123084942</v>
       </c>
       <c r="B11" t="n">
         <v>77694</v>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460885</v>
+        <v>460739</v>
       </c>
       <c r="R11" t="n">
-        <v>6866626</v>
+        <v>6866616</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123083574</v>
+        <v>123083226</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460893</v>
+        <v>460899</v>
       </c>
       <c r="R12" t="n">
-        <v>6866619</v>
+        <v>6866720</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123084899</v>
+        <v>123084785</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>79355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460751</v>
+        <v>460787</v>
       </c>
       <c r="R13" t="n">
-        <v>6866595</v>
+        <v>6866602</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123084848</v>
+        <v>123083889</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460770</v>
+        <v>460883</v>
       </c>
       <c r="R2" t="n">
-        <v>6866610</v>
+        <v>6866590</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083427</v>
+        <v>123084785</v>
       </c>
       <c r="B3" t="n">
-        <v>77694</v>
+        <v>79355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460885</v>
+        <v>460787</v>
       </c>
       <c r="R3" t="n">
-        <v>6866626</v>
+        <v>6866602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083574</v>
+        <v>123084224</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460893</v>
+        <v>460857</v>
       </c>
       <c r="R4" t="n">
-        <v>6866619</v>
+        <v>6866603</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123083889</v>
+        <v>123083427</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>77694</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460883</v>
+        <v>460885</v>
       </c>
       <c r="R6" t="n">
-        <v>6866590</v>
+        <v>6866626</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084224</v>
+        <v>123083226</v>
       </c>
       <c r="B7" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460857</v>
+        <v>460899</v>
       </c>
       <c r="R7" t="n">
-        <v>6866603</v>
+        <v>6866720</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123085253</v>
+        <v>123084899</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460766</v>
+        <v>460751</v>
       </c>
       <c r="R8" t="n">
-        <v>6866660</v>
+        <v>6866595</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084843</v>
+        <v>123085253</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460770</v>
+        <v>460766</v>
       </c>
       <c r="R9" t="n">
-        <v>6866610</v>
+        <v>6866660</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123084899</v>
+        <v>123084843</v>
       </c>
       <c r="B10" t="n">
         <v>78503</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460751</v>
+        <v>460770</v>
       </c>
       <c r="R10" t="n">
-        <v>6866595</v>
+        <v>6866610</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084942</v>
+        <v>123084848</v>
       </c>
       <c r="B11" t="n">
-        <v>77694</v>
+        <v>78502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460739</v>
+        <v>460770</v>
       </c>
       <c r="R11" t="n">
-        <v>6866616</v>
+        <v>6866610</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123083226</v>
+        <v>123084942</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>77694</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460899</v>
+        <v>460739</v>
       </c>
       <c r="R12" t="n">
-        <v>6866720</v>
+        <v>6866616</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123084785</v>
+        <v>123083574</v>
       </c>
       <c r="B13" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460787</v>
+        <v>460893</v>
       </c>
       <c r="R13" t="n">
-        <v>6866602</v>
+        <v>6866619</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123083889</v>
+        <v>123083427</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>77694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460883</v>
+        <v>460885</v>
       </c>
       <c r="R2" t="n">
-        <v>6866590</v>
+        <v>6866626</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123084785</v>
+        <v>123084848</v>
       </c>
       <c r="B3" t="n">
-        <v>79355</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460787</v>
+        <v>460770</v>
       </c>
       <c r="R3" t="n">
-        <v>6866602</v>
+        <v>6866610</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123084224</v>
+        <v>123085253</v>
       </c>
       <c r="B4" t="n">
         <v>78502</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460857</v>
+        <v>460766</v>
       </c>
       <c r="R4" t="n">
-        <v>6866603</v>
+        <v>6866660</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123084743</v>
+        <v>123083226</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460789</v>
+        <v>460899</v>
       </c>
       <c r="R5" t="n">
-        <v>6866588</v>
+        <v>6866720</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123083427</v>
+        <v>123083574</v>
       </c>
       <c r="B6" t="n">
-        <v>77694</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460885</v>
+        <v>460893</v>
       </c>
       <c r="R6" t="n">
-        <v>6866626</v>
+        <v>6866619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123083226</v>
+        <v>123084899</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460899</v>
+        <v>460751</v>
       </c>
       <c r="R7" t="n">
-        <v>6866720</v>
+        <v>6866595</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123084899</v>
+        <v>123083889</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460751</v>
+        <v>460883</v>
       </c>
       <c r="R8" t="n">
-        <v>6866595</v>
+        <v>6866590</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123085253</v>
+        <v>123084843</v>
       </c>
       <c r="B9" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460766</v>
+        <v>460770</v>
       </c>
       <c r="R9" t="n">
-        <v>6866660</v>
+        <v>6866610</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123084843</v>
+        <v>123084224</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460770</v>
+        <v>460857</v>
       </c>
       <c r="R10" t="n">
-        <v>6866610</v>
+        <v>6866603</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084848</v>
+        <v>123084743</v>
       </c>
       <c r="B11" t="n">
         <v>78502</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460770</v>
+        <v>460789</v>
       </c>
       <c r="R11" t="n">
-        <v>6866610</v>
+        <v>6866588</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123083574</v>
+        <v>123084785</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460893</v>
+        <v>460787</v>
       </c>
       <c r="R13" t="n">
-        <v>6866619</v>
+        <v>6866602</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123083427</v>
+        <v>123084843</v>
       </c>
       <c r="B2" t="n">
-        <v>77694</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460885</v>
+        <v>460770</v>
       </c>
       <c r="R2" t="n">
-        <v>6866626</v>
+        <v>6866610</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123084848</v>
+        <v>123083226</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460770</v>
+        <v>460899</v>
       </c>
       <c r="R3" t="n">
-        <v>6866610</v>
+        <v>6866720</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123085253</v>
+        <v>123084743</v>
       </c>
       <c r="B4" t="n">
         <v>78502</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460766</v>
+        <v>460789</v>
       </c>
       <c r="R4" t="n">
-        <v>6866660</v>
+        <v>6866588</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123083226</v>
+        <v>123084224</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460899</v>
+        <v>460857</v>
       </c>
       <c r="R5" t="n">
-        <v>6866720</v>
+        <v>6866603</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123083574</v>
+        <v>123084848</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460893</v>
+        <v>460770</v>
       </c>
       <c r="R6" t="n">
-        <v>6866619</v>
+        <v>6866610</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084899</v>
+        <v>123083889</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460751</v>
+        <v>460883</v>
       </c>
       <c r="R7" t="n">
-        <v>6866595</v>
+        <v>6866590</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123083889</v>
+        <v>123084899</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460883</v>
+        <v>460751</v>
       </c>
       <c r="R8" t="n">
-        <v>6866590</v>
+        <v>6866595</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084843</v>
+        <v>123084942</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>77694</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460770</v>
+        <v>460739</v>
       </c>
       <c r="R9" t="n">
-        <v>6866610</v>
+        <v>6866616</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123084224</v>
+        <v>123085253</v>
       </c>
       <c r="B10" t="n">
         <v>78502</v>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460857</v>
+        <v>460766</v>
       </c>
       <c r="R10" t="n">
-        <v>6866603</v>
+        <v>6866660</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084743</v>
+        <v>123084785</v>
       </c>
       <c r="B11" t="n">
-        <v>78502</v>
+        <v>79355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460789</v>
+        <v>460787</v>
       </c>
       <c r="R11" t="n">
-        <v>6866588</v>
+        <v>6866602</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123084942</v>
+        <v>123083427</v>
       </c>
       <c r="B12" t="n">
         <v>77694</v>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460739</v>
+        <v>460885</v>
       </c>
       <c r="R12" t="n">
-        <v>6866616</v>
+        <v>6866626</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123084785</v>
+        <v>123083574</v>
       </c>
       <c r="B13" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460787</v>
+        <v>460893</v>
       </c>
       <c r="R13" t="n">
-        <v>6866602</v>
+        <v>6866619</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123084843</v>
+        <v>123084224</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460770</v>
+        <v>460857</v>
       </c>
       <c r="R2" t="n">
-        <v>6866610</v>
+        <v>6866603</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083226</v>
+        <v>123084848</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460899</v>
+        <v>460770</v>
       </c>
       <c r="R3" t="n">
-        <v>6866720</v>
+        <v>6866610</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123084743</v>
+        <v>123085253</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460789</v>
+        <v>460766</v>
       </c>
       <c r="R4" t="n">
-        <v>6866588</v>
+        <v>6866660</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123084224</v>
+        <v>123083226</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460857</v>
+        <v>460899</v>
       </c>
       <c r="R5" t="n">
-        <v>6866603</v>
+        <v>6866720</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123084848</v>
+        <v>123084785</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>79358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460770</v>
+        <v>460787</v>
       </c>
       <c r="R6" t="n">
-        <v>6866610</v>
+        <v>6866602</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123083889</v>
+        <v>123084843</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460883</v>
+        <v>460770</v>
       </c>
       <c r="R7" t="n">
-        <v>6866590</v>
+        <v>6866610</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1290,7 +1290,7 @@
         <v>123084899</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084942</v>
+        <v>123083889</v>
       </c>
       <c r="B9" t="n">
-        <v>77694</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460739</v>
+        <v>460883</v>
       </c>
       <c r="R9" t="n">
-        <v>6866616</v>
+        <v>6866590</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123085253</v>
+        <v>123083427</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>77697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460766</v>
+        <v>460885</v>
       </c>
       <c r="R10" t="n">
-        <v>6866660</v>
+        <v>6866626</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084785</v>
+        <v>123084942</v>
       </c>
       <c r="B11" t="n">
-        <v>79355</v>
+        <v>77697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460787</v>
+        <v>460739</v>
       </c>
       <c r="R11" t="n">
-        <v>6866602</v>
+        <v>6866616</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123083427</v>
+        <v>123083574</v>
       </c>
       <c r="B12" t="n">
-        <v>77694</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460885</v>
+        <v>460893</v>
       </c>
       <c r="R12" t="n">
-        <v>6866626</v>
+        <v>6866619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123083574</v>
+        <v>123084743</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460893</v>
+        <v>460789</v>
       </c>
       <c r="R13" t="n">
-        <v>6866619</v>
+        <v>6866588</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123084224</v>
+        <v>123085253</v>
       </c>
       <c r="B2" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460857</v>
+        <v>460766</v>
       </c>
       <c r="R2" t="n">
-        <v>6866603</v>
+        <v>6866660</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123084848</v>
+        <v>123083889</v>
       </c>
       <c r="B3" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460770</v>
+        <v>460883</v>
       </c>
       <c r="R3" t="n">
-        <v>6866610</v>
+        <v>6866590</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123085253</v>
+        <v>123084785</v>
       </c>
       <c r="B4" t="n">
-        <v>78505</v>
+        <v>79360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460766</v>
+        <v>460787</v>
       </c>
       <c r="R4" t="n">
-        <v>6866660</v>
+        <v>6866602</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123083226</v>
+        <v>123084843</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460899</v>
+        <v>460770</v>
       </c>
       <c r="R5" t="n">
-        <v>6866720</v>
+        <v>6866610</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123084785</v>
+        <v>123084743</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460787</v>
+        <v>460789</v>
       </c>
       <c r="R6" t="n">
-        <v>6866602</v>
+        <v>6866588</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084843</v>
+        <v>123084224</v>
       </c>
       <c r="B7" t="n">
-        <v>78506</v>
+        <v>78507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460770</v>
+        <v>460857</v>
       </c>
       <c r="R7" t="n">
-        <v>6866610</v>
+        <v>6866603</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123084899</v>
+        <v>123083226</v>
       </c>
       <c r="B8" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460751</v>
+        <v>460899</v>
       </c>
       <c r="R8" t="n">
-        <v>6866595</v>
+        <v>6866720</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123083889</v>
+        <v>123084942</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460883</v>
+        <v>460739</v>
       </c>
       <c r="R9" t="n">
-        <v>6866590</v>
+        <v>6866616</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123083427</v>
+        <v>123084899</v>
       </c>
       <c r="B10" t="n">
-        <v>77697</v>
+        <v>78508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460885</v>
+        <v>460751</v>
       </c>
       <c r="R10" t="n">
-        <v>6866626</v>
+        <v>6866595</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084942</v>
+        <v>123084848</v>
       </c>
       <c r="B11" t="n">
-        <v>77697</v>
+        <v>78507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460739</v>
+        <v>460770</v>
       </c>
       <c r="R11" t="n">
-        <v>6866616</v>
+        <v>6866610</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123083574</v>
+        <v>123083427</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>77699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460893</v>
+        <v>460885</v>
       </c>
       <c r="R12" t="n">
-        <v>6866619</v>
+        <v>6866626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123084743</v>
+        <v>123083574</v>
       </c>
       <c r="B13" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460789</v>
+        <v>460893</v>
       </c>
       <c r="R13" t="n">
-        <v>6866588</v>
+        <v>6866619</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123085253</v>
+        <v>123083889</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460766</v>
+        <v>460883</v>
       </c>
       <c r="R2" t="n">
-        <v>6866660</v>
+        <v>6866590</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083889</v>
+        <v>123083226</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460883</v>
+        <v>460899</v>
       </c>
       <c r="R3" t="n">
-        <v>6866590</v>
+        <v>6866720</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>123084785</v>
       </c>
       <c r="B4" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>123084843</v>
       </c>
       <c r="B5" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123084743</v>
+        <v>123084224</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460789</v>
+        <v>460857</v>
       </c>
       <c r="R6" t="n">
-        <v>6866588</v>
+        <v>6866603</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084224</v>
+        <v>123083574</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460857</v>
+        <v>460893</v>
       </c>
       <c r="R7" t="n">
-        <v>6866603</v>
+        <v>6866619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123083226</v>
+        <v>123084848</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460899</v>
+        <v>460770</v>
       </c>
       <c r="R8" t="n">
-        <v>6866720</v>
+        <v>6866610</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084942</v>
+        <v>123085253</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>78508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460739</v>
+        <v>460766</v>
       </c>
       <c r="R9" t="n">
-        <v>6866616</v>
+        <v>6866660</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123084899</v>
+        <v>123083427</v>
       </c>
       <c r="B10" t="n">
-        <v>78508</v>
+        <v>77700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460751</v>
+        <v>460885</v>
       </c>
       <c r="R10" t="n">
-        <v>6866595</v>
+        <v>6866626</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123084848</v>
+        <v>123084743</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460770</v>
+        <v>460789</v>
       </c>
       <c r="R11" t="n">
-        <v>6866610</v>
+        <v>6866588</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123083427</v>
+        <v>123084942</v>
       </c>
       <c r="B12" t="n">
-        <v>77699</v>
+        <v>77700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460885</v>
+        <v>460739</v>
       </c>
       <c r="R12" t="n">
-        <v>6866626</v>
+        <v>6866616</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123083574</v>
+        <v>123084899</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460893</v>
+        <v>460751</v>
       </c>
       <c r="R13" t="n">
-        <v>6866619</v>
+        <v>6866595</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123084848</v>
+        <v>123084899</v>
       </c>
       <c r="B8" t="n">
-        <v>78511</v>
+        <v>78512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460770</v>
+        <v>460751</v>
       </c>
       <c r="R8" t="n">
-        <v>6866610</v>
+        <v>6866595</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123084899</v>
+        <v>123084848</v>
       </c>
       <c r="B9" t="n">
-        <v>78512</v>
+        <v>78511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460751</v>
+        <v>460770</v>
       </c>
       <c r="R9" t="n">
-        <v>6866595</v>
+        <v>6866610</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>

--- a/artfynd/A 49333-2024 artfynd.xlsx
+++ b/artfynd/A 49333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123083226</v>
+        <v>123083427</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>77709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460899</v>
+        <v>460885</v>
       </c>
       <c r="R2" t="n">
-        <v>6866720</v>
+        <v>6866626</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123083574</v>
+        <v>123083226</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460893</v>
+        <v>460899</v>
       </c>
       <c r="R3" t="n">
-        <v>6866619</v>
+        <v>6866720</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123083427</v>
+        <v>123083574</v>
       </c>
       <c r="B4" t="n">
-        <v>77703</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460885</v>
+        <v>460893</v>
       </c>
       <c r="R4" t="n">
-        <v>6866626</v>
+        <v>6866619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123084743</v>
+        <v>123084843</v>
       </c>
       <c r="B5" t="n">
-        <v>78511</v>
+        <v>78518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460789</v>
+        <v>460770</v>
       </c>
       <c r="R5" t="n">
-        <v>6866588</v>
+        <v>6866610</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123084224</v>
+        <v>123084743</v>
       </c>
       <c r="B6" t="n">
-        <v>78511</v>
+        <v>78517</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460857</v>
+        <v>460789</v>
       </c>
       <c r="R6" t="n">
-        <v>6866603</v>
+        <v>6866588</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123084785</v>
+        <v>123084224</v>
       </c>
       <c r="B7" t="n">
-        <v>79364</v>
+        <v>78517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460787</v>
+        <v>460857</v>
       </c>
       <c r="R7" t="n">
-        <v>6866602</v>
+        <v>6866603</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>123084899</v>
       </c>
       <c r="B8" t="n">
-        <v>78512</v>
+        <v>78518</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>123084848</v>
       </c>
       <c r="B9" t="n">
-        <v>78511</v>
+        <v>78517</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123083889</v>
+        <v>123084785</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460883</v>
+        <v>460787</v>
       </c>
       <c r="R10" t="n">
-        <v>6866590</v>
+        <v>6866602</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123085253</v>
+        <v>123083889</v>
       </c>
       <c r="B11" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460766</v>
+        <v>460883</v>
       </c>
       <c r="R11" t="n">
-        <v>6866660</v>
+        <v>6866590</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123084843</v>
+        <v>123084942</v>
       </c>
       <c r="B12" t="n">
-        <v>78512</v>
+        <v>77709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460770</v>
+        <v>460739</v>
       </c>
       <c r="R12" t="n">
-        <v>6866610</v>
+        <v>6866616</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123084942</v>
+        <v>123085253</v>
       </c>
       <c r="B13" t="n">
-        <v>77703</v>
+        <v>78517</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460739</v>
+        <v>460766</v>
       </c>
       <c r="R13" t="n">
-        <v>6866616</v>
+        <v>6866660</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
